--- a/ROUTE_2_PATH2_ADMIN_MBA_LIB_AIML_AUDI/PATH2_ANSWER_KEY.xlsx
+++ b/ROUTE_2_PATH2_ADMIN_MBA_LIB_AIML_AUDI/PATH2_ANSWER_KEY.xlsx
@@ -546,10 +546,10 @@
         <v>None</v>
       </c>
       <c r="F6" t="str">
-        <v>10 Answers &amp; Code: MB-BQ-2 (UPPERCASE ONLY)</v>
+        <v>10 Answers &amp; Code: MBA-BQ-2 (UPPERCASE ONLY)</v>
       </c>
       <c r="G6" t="str">
-        <v>Strict UPPERCASE regex &amp; normalize-space(.) = 'MB-BQ-2'</v>
+        <v>Strict UPPERCASE regex &amp; normalize-space(.) = 'MBA-BQ-2'</v>
       </c>
       <c r="H6" t="str">
         <v>No (All 10 Inputs MANDATORY)</v>
@@ -589,19 +589,19 @@
         <v>LIBRARY</v>
       </c>
       <c r="C8" t="str">
-        <v>QR Hunt &amp; Volunteer Code</v>
+        <v>QR Hunt</v>
       </c>
       <c r="D8" t="str">
-        <v>Scan hidden QR code in library, enter volunteer completion code</v>
+        <v>Scan hidden QR code in library</v>
       </c>
       <c r="E8" t="str">
         <v>None</v>
       </c>
       <c r="F8" t="str">
-        <v>Barcode: DUMB_FAKE &amp; Code: DUMB_FAKE (UPPERCASE ONLY)</v>
+        <v>Barcode: DUMB_FAKE (UPPERCASE ONLY)</v>
       </c>
       <c r="G8" t="str">
-        <v>Scanned value = 'DUMB_FAKE' &amp; normalize-space(.) = 'DUMB_FAKE'</v>
+        <v>Scanned value = 'DUMB_FAKE'</v>
       </c>
       <c r="H8" t="str">
         <v>Yes (Barcode Scan MANDATORY)</v>
